--- a/tools/importer/reports/import-microsoft-365.report.xlsx
+++ b/tools/importer/reports/import-microsoft-365.report.xlsx
@@ -94,7 +94,7 @@
     <t>microsoft-365</t>
   </si>
   <si>
-    <t>2026-03-20T21:23:34.867Z</t>
+    <t>2026-03-20T21:37:47.056Z</t>
   </si>
   <si>
     <t>Microsoft 365 for Individuals: Subscription for Productivity Apps</t>

--- a/tools/importer/reports/import-microsoft-365.report.xlsx
+++ b/tools/importer/reports/import-microsoft-365.report.xlsx
@@ -94,7 +94,7 @@
     <t>microsoft-365</t>
   </si>
   <si>
-    <t>2026-03-20T21:37:47.056Z</t>
+    <t>2026-03-21T00:05:52.486Z</t>
   </si>
   <si>
     <t>Microsoft 365 for Individuals: Subscription for Productivity Apps</t>

--- a/tools/importer/reports/import-microsoft-365.report.xlsx
+++ b/tools/importer/reports/import-microsoft-365.report.xlsx
@@ -94,7 +94,7 @@
     <t>microsoft-365</t>
   </si>
   <si>
-    <t>2026-03-21T00:05:52.486Z</t>
+    <t>2026-03-23T14:51:19.086Z</t>
   </si>
   <si>
     <t>Microsoft 365 for Individuals: Subscription for Productivity Apps</t>
